--- a/data/synthetic_survey_v2_SYNTHETIC.xlsx
+++ b/data/synthetic_survey_v2_SYNTHETIC.xlsx
@@ -551,7 +551,7 @@
     <t>SYNTHETIC DATA — NOT REAL RESPONDENTS</t>
   </si>
   <si>
-    <t>Generated by core/sample_data.py (seed 2026) to demonstrate the Team Anova × ZiffyHealth digital-trust analysis pipeline. It mirrors the survey instrument (v2, corrected) and follows a documented latent-variable model. Any statistic computed from it describes the simulation, not Indian digital-health users.</t>
+    <t>Generated by core/sample_data.py (seed 2026) to demonstrate the Team Anova × ZiffyHealth digital-trust analysis pipeline (method illustration only). Its demo instrument is NOT the Team Anova form, and it follows a documented latent-variable model. Any statistic computed from it describes the simulation, not Indian digital-health users.</t>
   </si>
 </sst>
 </file>
